--- a/docs/control-plane/05_SERVICE_INTEGRATION_REGISTRY.xlsx
+++ b/docs/control-plane/05_SERVICE_INTEGRATION_REGISTRY.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="160">
   <si>
     <t>05_SERVICE_INTEGRATION_REGISTRY</t>
   </si>
@@ -47,6 +47,12 @@
     <t>CRITICAL: NEVER STORE PASSWORDS, API KEYS, SERVICE-ROLE KEYS, PRIVATE CERTIFICATES, SMTP PASSWORDS, OR R2 SECRETS IN THIS WORKBOOK. USE SECURE ENVIRONMENT REFERENCES ONLY.</t>
   </si>
   <si>
+    <t>Canonical Production Subdomain</t>
+  </si>
+  <si>
+    <t>https://erp.arivahly.in (Parent domain: arivahly.in)</t>
+  </si>
+  <si>
     <t>AI Operating Constraint 1</t>
   </si>
   <si>
@@ -71,10 +77,16 @@
     <t>UNKNOWN means unknown. Do not guess. If a field is uncertain, record NEEDS_VERIFICATION.</t>
   </si>
   <si>
+    <t>MCP Security Boundary</t>
+  </si>
+  <si>
+    <t>MCP is DISABLED and BLOCKED from public routing. MCP tools must remain internal/local only.</t>
+  </si>
+  <si>
     <t>Last Audit Date</t>
   </si>
   <si>
-    <t>2026-09-05T13:10:00+05:30 (Release v1.1.2-online-production-hardened)</t>
+    <t>2026-09-05T13:20:00+05:30 (Release v1.1.2-online-production-hardened)</t>
   </si>
   <si>
     <t>Service_ID</t>
@@ -281,7 +293,7 @@
     <t>BLOCKED</t>
   </si>
   <si>
-    <t>Intentionally DISABLED in current release</t>
+    <t>Intentionally DISABLED in current release; MCP remains blocked</t>
   </si>
   <si>
     <t>Integration_ID</t>
@@ -332,7 +344,7 @@
     <t>TENANT-SCOPED</t>
   </si>
   <si>
-    <t>Verified webhook dispatcher</t>
+    <t>Verified webhook dispatcher on https://erp.arivahly.in/api/webhooks/dispatcher.php?provider=razorpay</t>
   </si>
   <si>
     <t>INT-002</t>
@@ -356,7 +368,7 @@
     <t>50 emails/min</t>
   </si>
   <si>
-    <t>Native server-side mail path</t>
+    <t>Native server-side mail path from admin@arivahly.in</t>
   </si>
   <si>
     <t>INT-003</t>
@@ -374,7 +386,7 @@
     <t>80 msgs/min</t>
   </si>
   <si>
-    <t>Configured via Admin Panel</t>
+    <t>Configured via Admin Panel on https://erp.arivahly.in</t>
   </si>
   <si>
     <t>Webhook_ID</t>
@@ -401,7 +413,7 @@
     <t>Razorpay</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/api/webhooks/dispatcher.php</t>
+    <t>https://erp.arivahly.in/api/webhooks/dispatcher.php</t>
   </si>
   <si>
     <t>payment.captured, subscription.charged</t>
@@ -470,10 +482,10 @@
     <t>EML-001</t>
   </si>
   <si>
-    <t>Hostinger SMTP (admin@maatarajewellers.shop)</t>
-  </si>
-  <si>
-    <t>admin@maatarajewellers.shop</t>
+    <t>Hostinger SMTP (admin@arivahly.in)</t>
+  </si>
+  <si>
+    <t>admin@arivahly.in</t>
   </si>
   <si>
     <t>support@arivahly.in</t>
@@ -939,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1024,6 +1036,22 @@
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1049,335 +1077,335 @@
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="52" customWidth="1"/>
+    <col min="13" max="13" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="K3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="M3" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1402,171 +1430,171 @@
     <col min="9" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="32" customWidth="1"/>
+    <col min="13" max="13" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="K3" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="K4" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1597,125 +1625,125 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="J3" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1730,8 +1758,8 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="54" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
@@ -1745,90 +1773,90 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
